--- a/314e-ig/output/StructureDefinition-condition-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-condition-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -314,7 +314,7 @@
     <t>Condition.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-condition-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-condition-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-condition-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-condition-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-condition-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-condition-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-condition-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-condition-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -796,7 +796,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/group-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -824,7 +824,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -924,7 +924,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1051,7 +1051,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|DiagnosticReport|Observation) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1485,7 +1485,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="156.08203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-condition-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-condition-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-condition-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-condition-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="369">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,6 +516,22 @@
     <t>Applied at the root level of any resource. Used to capture supplementary
 or non-standard information related to a FHIR resource that is not
 represented by the core FHIR elements or existing profiles.</t>
+  </si>
+  <si>
+    <t>Condition.extension:assertedDate</t>
+  </si>
+  <si>
+    <t>assertedDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/condition-assertedDate-314e}
+</t>
+  </si>
+  <si>
+    <t>Date the condition, problem, or diagnosis was asserted</t>
+  </si>
+  <si>
+    <t>When the asserter identified the allergy, intolerance, condition, problem, or diagnosis or other event, situation, issue, or clinical concept that may have risen to a level of or remains a concern.  For example, when the patient experiences chest pain, the asserted date represents when the clinician began following the chest pain - not when the patient experienced the chest pain.  Asserted date supports the recognition that information is not always entered in a system immediately.  Assertion and recording are different acts, so asserted date and recorded date are semantically different. However, they may be the same date and close in time.  If this difference is significant for your use case, assertion date may be useful.</t>
   </si>
   <si>
     <t>Condition.modifierExtension</t>
@@ -1472,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP41"/>
+  <dimension ref="A1:AP42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="31.5625" customWidth="true" bestFit="true"/>
@@ -2963,43 +2979,41 @@
         <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="O13" t="s" s="2">
-        <v>163</v>
-      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>20</v>
       </c>
@@ -3047,7 +3061,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3056,7 +3070,7 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>141</v>
@@ -3071,7 +3085,7 @@
         <v>20</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>133</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>20</v>
@@ -3082,14 +3096,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3102,25 +3116,25 @@
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3169,7 +3183,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3181,10 +3195,10 @@
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
@@ -3193,10 +3207,10 @@
         <v>20</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>20</v>
@@ -3204,10 +3218,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3218,30 +3232,32 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3265,13 +3281,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3289,34 +3305,34 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>20</v>
@@ -3324,10 +3340,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3350,16 +3366,16 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3385,31 +3401,31 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3418,36 +3434,36 @@
         <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>198</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3458,28 +3474,28 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3505,13 +3521,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3529,45 +3545,45 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI17" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>20</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3578,7 +3594,7 @@
         <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3590,16 +3606,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3625,13 +3641,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>114</v>
+        <v>208</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3649,13 +3665,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3667,31 +3683,31 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3707,21 +3723,21 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3745,13 +3761,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>224</v>
+        <v>114</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3769,7 +3785,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3784,41 +3800,41 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3830,18 +3846,18 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -3865,37 +3881,37 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Y20" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>233</v>
-      </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -3904,41 +3920,41 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>20</v>
+        <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>243</v>
+        <v>20</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3950,18 +3966,18 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>244</v>
+        <v>180</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -3985,13 +4001,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4009,13 +4025,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4024,38 +4040,38 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>251</v>
+        <v>20</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>20</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>20</v>
+        <v>248</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
@@ -4070,18 +4086,18 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4129,10 +4145,10 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>90</v>
@@ -4144,19 +4160,19 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4164,10 +4180,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4190,16 +4206,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4249,7 +4265,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4264,19 +4280,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4284,10 +4300,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4307,19 +4323,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4369,7 +4385,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4378,25 +4394,25 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>274</v>
+        <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>20</v>
+        <v>272</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -4404,10 +4420,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4427,18 +4443,20 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4487,7 +4505,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4496,7 +4514,7 @@
         <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>20</v>
+        <v>279</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>102</v>
@@ -4508,13 +4526,13 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -4522,10 +4540,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4548,13 +4566,13 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4605,7 +4623,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4626,13 +4644,13 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>20</v>
+        <v>286</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>20</v>
@@ -4640,10 +4658,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4666,7 +4684,7 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>291</v>
@@ -4723,7 +4741,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4744,13 +4762,13 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>20</v>
@@ -4758,10 +4776,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4772,7 +4790,7 @@
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4781,16 +4799,16 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4841,34 +4859,34 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>20</v>
@@ -4876,10 +4894,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4890,7 +4908,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4902,13 +4920,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4959,31 +4977,31 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -4994,21 +5012,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5020,7 +5038,7 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>309</v>
@@ -5028,9 +5046,7 @@
       <c r="M30" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5085,13 +5101,13 @@
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5103,7 +5119,7 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5114,14 +5130,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5134,10 +5150,10 @@
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>135</v>
@@ -5149,11 +5165,9 @@
         <v>315</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5225,7 +5239,7 @@
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>133</v>
+        <v>312</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5243,35 +5257,39 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5295,55 +5313,55 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>320</v>
+        <v>20</v>
       </c>
       <c r="Z32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>317</v>
-      </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>230</v>
+        <v>133</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5354,10 +5372,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5368,7 +5386,7 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5380,13 +5398,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>325</v>
+        <v>180</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5413,13 +5431,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>20</v>
+        <v>325</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5437,16 +5455,16 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
@@ -5455,13 +5473,13 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>328</v>
+        <v>235</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -5486,7 +5504,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5498,13 +5516,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5531,13 +5549,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5561,10 +5579,10 @@
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>102</v>
@@ -5579,7 +5597,7 @@
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -5590,10 +5608,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5604,7 +5622,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5616,17 +5634,15 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>297</v>
+        <v>180</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5651,13 +5667,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5675,31 +5691,31 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -5710,10 +5726,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5724,7 +5740,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5736,15 +5752,17 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5793,19 +5811,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>20</v>
+        <v>344</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -5817,7 +5835,7 @@
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -5828,21 +5846,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5854,7 +5872,7 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>309</v>
@@ -5862,9 +5880,7 @@
       <c r="M37" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N37" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5919,13 +5935,13 @@
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -5937,7 +5953,7 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -5948,14 +5964,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5968,10 +5984,10 @@
         <v>20</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>135</v>
@@ -5983,11 +5999,9 @@
         <v>315</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6059,7 +6073,7 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>133</v>
+        <v>312</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6070,14 +6084,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6090,22 +6104,26 @@
         <v>20</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6129,13 +6147,13 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>224</v>
+        <v>20</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6153,7 +6171,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6162,25 +6180,25 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>349</v>
+        <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>351</v>
+        <v>133</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>20</v>
@@ -6188,10 +6206,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6214,13 +6232,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6247,13 +6265,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>20</v>
+        <v>353</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6271,7 +6289,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6280,25 +6298,25 @@
         <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -6306,10 +6324,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6329,16 +6347,16 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6389,7 +6407,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6398,27 +6416,145 @@
         <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>20</v>
+        <v>354</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="B42" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K42" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AO41" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP41" t="s" s="2">
+      <c r="L42" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
